--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Llama-3.3-70B-Instruct/aae/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Llama-3.3-70B-Instruct/aae/total_votes_file.xlsx
@@ -433,10 +433,10 @@
         <v>17</v>
       </c>
       <c r="D2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -456,10 +456,10 @@
         <v>387</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3">
         <v>426</v>
